--- a/Data_clean/MCAS/Estados_US/Edos_USA_2016/WEST_VIRGINIA_2016.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2016/WEST_VIRGINIA_2016.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D480"/>
+  <dimension ref="A1:D143"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Cacahoatán</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Chamula</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Escuintla</t>
@@ -465,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Huixtán</t>
@@ -478,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -491,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -504,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Mazatán</t>
@@ -517,9 +557,14 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Salto de Agua</t>
+          <t>Salto De Agua</t>
         </is>
       </c>
       <c r="C12">
@@ -530,9 +575,14 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>San Cristóbal de las Casas</t>
+          <t>San Cristóbal De Las Casas</t>
         </is>
       </c>
       <c r="C13">
@@ -543,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Tapalapa</t>
@@ -556,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Teopisca</t>
@@ -569,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Unión Juárez</t>
@@ -582,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Villa Corzo</t>
@@ -595,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -626,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Total</t>
@@ -641,7 +721,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -657,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -670,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -683,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -696,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -709,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Xochimilco</t>
@@ -722,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Total</t>
@@ -753,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Total</t>
@@ -768,7 +883,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -784,9 +899,14 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>San Antonio la Isla</t>
+          <t>San Antonio La Isla</t>
         </is>
       </c>
       <c r="C31">
@@ -797,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Sultepec</t>
@@ -810,9 +935,14 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C33">
@@ -823,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Tlatlaya</t>
@@ -836,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -849,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Total</t>
@@ -880,9 +1025,14 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna de la Independencia Nacional</t>
+          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
         </is>
       </c>
       <c r="C38">
@@ -893,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>León</t>
@@ -906,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Manuel Doblado</t>
@@ -919,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -932,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Salamanca</t>
@@ -945,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Salvatierra</t>
@@ -958,9 +1133,14 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Silao de la Victoria</t>
+          <t>Silao De La Victoria</t>
         </is>
       </c>
       <c r="C44">
@@ -971,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -984,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1004,7 +1194,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cutzamala de Pinzón</t>
+          <t>Cutzamala De Pinzón</t>
         </is>
       </c>
       <c r="C47">
@@ -1015,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Metlatónoc</t>
@@ -1028,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -1041,9 +1241,14 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C50">
@@ -1054,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1085,9 +1295,14 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mineral del Chico</t>
+          <t>Mineral Del Chico</t>
         </is>
       </c>
       <c r="C53">
@@ -1098,9 +1313,14 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C54">
@@ -1111,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Zimapán</t>
@@ -1124,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1155,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1168,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -1181,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1212,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Coeneo</t>
@@ -1225,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Epitacio Huerta</t>
@@ -1238,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -1251,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Paracho</t>
@@ -1264,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>San Lucas</t>
@@ -1277,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Tangancícuaro</t>
@@ -1290,9 +1565,14 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tiquicheo de Nicolás Romero</t>
+          <t>Tiquicheo De Nicolás Romero</t>
         </is>
       </c>
       <c r="C68">
@@ -1303,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1334,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -1347,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Emiliano Zapata</t>
@@ -1360,9 +1655,14 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Puente de Ixtla</t>
+          <t>Puente De Ixtla</t>
         </is>
       </c>
       <c r="C73">
@@ -1373,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1404,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1424,7 +1734,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Acatlán de Pérez Figueroa</t>
+          <t>Acatlán De Pérez Figueroa</t>
         </is>
       </c>
       <c r="C77">
@@ -1435,9 +1745,14 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Ejutla de Crespo</t>
+          <t>Heroica Ciudad De Ejutla De Crespo</t>
         </is>
       </c>
       <c r="C78">
@@ -1448,9 +1763,14 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Tlaxiaco</t>
+          <t>Heroica Ciudad De Tlaxiaco</t>
         </is>
       </c>
       <c r="C79">
@@ -1461,9 +1781,14 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Juchitán de Zaragoza</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C80">
@@ -1474,9 +1799,14 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C81">
@@ -1487,9 +1817,14 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Putla Villa de Guerrero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C82">
@@ -1500,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>San Juan Colorado</t>
@@ -1513,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>San Pedro Pochutla</t>
@@ -1526,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>San Vicente Coatlán</t>
@@ -1539,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Santa María Jacatepec</t>
@@ -1552,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Santa María Zacatepec</t>
@@ -1565,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -1578,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Santos Reyes Nopala</t>
@@ -1591,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Silacayoápam</t>
@@ -1604,9 +1979,14 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Villa de Zaachila</t>
+          <t>Villa De Zaachila</t>
         </is>
       </c>
       <c r="C91">
@@ -1617,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1648,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Huaquechula</t>
@@ -1661,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>San Pedro Cholula</t>
@@ -1674,9 +2069,14 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>San Salvador el Verde</t>
+          <t>San Salvador El Verde</t>
         </is>
       </c>
       <c r="C96">
@@ -1687,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -1700,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1720,7 +2130,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Pinal de Amoles</t>
+          <t>Pinal De Amoles</t>
         </is>
       </c>
       <c r="C99">
@@ -1731,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -1744,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1775,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Huehuetlán</t>
@@ -1788,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Matehuala</t>
@@ -1801,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Moctezuma</t>
@@ -1814,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -1827,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -1840,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Tampamolón Corona</t>
@@ -1853,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Xilitla</t>
@@ -1866,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1897,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Choix</t>
@@ -1910,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1941,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1972,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2003,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>González</t>
@@ -2016,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Mainero</t>
@@ -2029,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Valle Hermoso</t>
@@ -2042,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2073,9 +2573,14 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Amatlán de los Reyes</t>
+          <t>Amatlán De Los Reyes</t>
         </is>
       </c>
       <c r="C124">
@@ -2086,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Calcahualco</t>
@@ -2099,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Coatzacoalcos</t>
@@ -2112,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Comapa</t>
@@ -2125,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -2138,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Espinal</t>
@@ -2151,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Huatusco</t>
@@ -2164,9 +2699,14 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C131">
@@ -2177,9 +2717,14 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C132">
@@ -2190,9 +2735,14 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Nanchital de Lázaro Cárdenas del Río</t>
+          <t>Nanchital De Lázaro Cárdenas Del Río</t>
         </is>
       </c>
       <c r="C133">
@@ -2203,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Playa Vicente</t>
@@ -2216,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>San Andrés Tuxtla</t>
@@ -2229,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Tempoal</t>
@@ -2242,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -2255,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Yanga</t>
@@ -2268,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Zongolica</t>
@@ -2281,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2312,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2335,76 +2925,6 @@
       </c>
       <c r="D143">
         <v>1</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 814,748</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Marzo de 2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 1,114,005</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>Junio de 2016</t>
-        </is>
       </c>
     </row>
   </sheetData>
